--- a/E/RPROCL1.xlsx
+++ b/E/RPROCL1.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
   <si>
     <t/>
   </si>
@@ -32,36 +32,6 @@
   </si>
   <si>
     <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10008651</t>
-  </si>
-  <si>
-    <t>S/G CHK.NGT ORGNL400</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10017288</t>
-  </si>
-  <si>
-    <t>SO GOOD SPIC.WING400</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20139320</t>
-  </si>
-  <si>
-    <t>SG CRSPY CN HOT 400G</t>
-  </si>
-  <si>
-    <t>112</t>
   </si>
 </sst>
 </file>
@@ -454,13 +424,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="5" max="5" width="5" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -501,66 +471,6 @@
         <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/E/RPROCL1.xlsx
+++ b/E/RPROCL1.xlsx
@@ -11,27 +11,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
   <si>
     <t/>
   </si>
   <si>
-    <t>20135228</t>
-  </si>
-  <si>
-    <t>AICE CRISPY BALLS 65</t>
+    <t>20024079</t>
+  </si>
+  <si>
+    <t>TELUR AYM NEGERI BKL</t>
   </si>
   <si>
     <t>RPROCL1</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
+    <t>1</t>
+  </si>
+  <si>
+    <t>PT,(E-1H)</t>
   </si>
 </sst>
 </file>
@@ -429,8 +426,7 @@
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="5" max="5" width="4" customWidth="1"/>
+    <col min="4" max="5" width="3" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -468,10 +464,10 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/E/RPROCL1.xlsx
+++ b/E/RPROCL1.xlsx
@@ -11,24 +11,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
   <si>
     <t/>
   </si>
   <si>
-    <t>20024079</t>
-  </si>
-  <si>
-    <t>TELUR AYM NEGERI BKL</t>
+    <t>10037640</t>
+  </si>
+  <si>
+    <t>WALL'S FEAST VNILA65</t>
   </si>
   <si>
     <t>RPROCL1</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>PT,(E-1H)</t>
+    <t>2</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10037632</t>
+  </si>
+  <si>
+    <t>WALL'S FEAST CKLT.65</t>
+  </si>
+  <si>
+    <t>46</t>
   </si>
 </sst>
 </file>
@@ -421,12 +433,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="4" max="5" width="3" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -464,10 +477,30 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
+      <c r="E3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/E/RPROCL1.xlsx
+++ b/E/RPROCL1.xlsx
@@ -11,18 +11,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
   <si>
     <t/>
   </si>
   <si>
+    <t>20024079</t>
+  </si>
+  <si>
+    <t>TELUR AYM NEGERI BKL</t>
+  </si>
+  <si>
+    <t>RPROCL1</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>PT,(E-1H)</t>
+  </si>
+  <si>
     <t>10037640</t>
   </si>
   <si>
     <t>WALL'S FEAST VNILA65</t>
-  </si>
-  <si>
-    <t>RPROCL1</t>
   </si>
   <si>
     <t>2</t>
@@ -433,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -477,30 +489,50 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/E/RPROCL1.xlsx
+++ b/E/RPROCL1.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="11">
   <si>
     <t/>
   </si>
@@ -31,28 +31,19 @@
     <t>PT,(E-1H)</t>
   </si>
   <si>
-    <t>10037640</t>
-  </si>
-  <si>
-    <t>WALL'S FEAST VNILA65</t>
+    <t>20008252</t>
+  </si>
+  <si>
+    <t>WALL'S P/P SHAKY 140</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>45</t>
+    <t>31</t>
   </si>
   <si>
     <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10037632</t>
-  </si>
-  <si>
-    <t>WALL'S FEAST CKLT.65</t>
-  </si>
-  <si>
-    <t>46</t>
   </si>
 </sst>
 </file>
@@ -445,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -515,26 +506,6 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/RPROCL1.xlsx
+++ b/E/RPROCL1.xlsx
@@ -11,39 +11,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
   <si>
     <t/>
   </si>
   <si>
-    <t>20024079</t>
-  </si>
-  <si>
-    <t>TELUR AYM NEGERI BKL</t>
+    <t>10005038</t>
+  </si>
+  <si>
+    <t>WALLS PPL CHO-VNL 90</t>
   </si>
   <si>
     <t>RPROCL1</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>PT,(E-1H)</t>
-  </si>
-  <si>
-    <t>20008252</t>
-  </si>
-  <si>
-    <t>WALL'S P/P SHAKY 140</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
-    <t>31</t>
+    <t>32</t>
   </si>
   <si>
     <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10005039</t>
+  </si>
+  <si>
+    <t>WALLS PPL STW-VNL 90</t>
+  </si>
+  <si>
+    <t>33</t>
   </si>
 </sst>
 </file>
@@ -480,30 +477,30 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/E/RPROCL1.xlsx
+++ b/E/RPROCL1.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
   <si>
     <t/>
   </si>
   <si>
-    <t>10005038</t>
-  </si>
-  <si>
-    <t>WALLS PPL CHO-VNL 90</t>
+    <t>20032368</t>
+  </si>
+  <si>
+    <t>WALL'S MAGNUM ALMD80</t>
   </si>
   <si>
     <t>RPROCL1</t>
@@ -28,19 +28,16 @@
     <t>2</t>
   </si>
   <si>
-    <t>32</t>
+    <t>1</t>
   </si>
   <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>10005039</t>
-  </si>
-  <si>
-    <t>WALLS PPL STW-VNL 90</t>
-  </si>
-  <si>
-    <t>33</t>
+    <t>20032366</t>
+  </si>
+  <si>
+    <t>WALL'S MAGNUM CLAS80</t>
   </si>
 </sst>
 </file>
@@ -438,8 +435,7 @@
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="5" max="5" width="4" customWidth="1"/>
+    <col min="4" max="5" width="3" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -497,7 +493,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>6</v>

--- a/E/RPROCL1.xlsx
+++ b/E/RPROCL1.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
   <si>
     <t/>
   </si>
@@ -38,6 +38,18 @@
   </si>
   <si>
     <t>WALL'S MAGNUM CLAS80</t>
+  </si>
+  <si>
+    <t>20140182</t>
+  </si>
+  <si>
+    <t>CMP HULA MAX K.HJ 65</t>
+  </si>
+  <si>
+    <t>147</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
   </si>
 </sst>
 </file>
@@ -430,12 +442,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="4" max="5" width="3" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="5" max="5" width="5" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -499,6 +512,26 @@
         <v>6</v>
       </c>
     </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/RPROCL1.xlsx
+++ b/E/RPROCL1.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
   <si>
     <t/>
   </si>
   <si>
-    <t>20032368</t>
-  </si>
-  <si>
-    <t>WALL'S MAGNUM ALMD80</t>
+    <t>20129821</t>
+  </si>
+  <si>
+    <t>MAGNUM MATCHA.CRBL80</t>
   </si>
   <si>
     <t>RPROCL1</t>
@@ -28,28 +28,19 @@
     <t>2</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20032366</t>
-  </si>
-  <si>
-    <t>WALL'S MAGNUM CLAS80</t>
-  </si>
-  <si>
-    <t>20140182</t>
-  </si>
-  <si>
-    <t>CMP HULA MAX K.HJ 65</t>
-  </si>
-  <si>
-    <t>147</t>
+    <t>47</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20134689</t>
+  </si>
+  <si>
+    <t>MAGNUM MNGO YOGHRT80</t>
+  </si>
+  <si>
+    <t>92</t>
   </si>
 </sst>
 </file>
@@ -442,13 +433,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="5" max="5" width="5" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -506,30 +497,10 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/E/RPROCL1.xlsx
+++ b/E/RPROCL1.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="11">
   <si>
     <t/>
   </si>
   <si>
-    <t>20129821</t>
-  </si>
-  <si>
-    <t>MAGNUM MATCHA.CRBL80</t>
+    <t>20113120</t>
+  </si>
+  <si>
+    <t>AICE CHOCO ALMOND 90</t>
   </si>
   <si>
     <t>RPROCL1</t>
@@ -28,19 +28,22 @@
     <t>2</t>
   </si>
   <si>
-    <t>47</t>
+    <t>15</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20134511</t>
+  </si>
+  <si>
+    <t>AICE CLSC CHO ALMD90</t>
+  </si>
+  <si>
+    <t>91</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20134689</t>
-  </si>
-  <si>
-    <t>MAGNUM MNGO YOGHRT80</t>
-  </si>
-  <si>
-    <t>92</t>
   </si>
 </sst>
 </file>
@@ -500,7 +503,7 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/E/RPROCL1.xlsx
+++ b/E/RPROCL1.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
   <si>
     <t/>
   </si>
   <si>
-    <t>20113120</t>
-  </si>
-  <si>
-    <t>AICE CHOCO ALMOND 90</t>
+    <t>20094387</t>
+  </si>
+  <si>
+    <t>CRNETTO SLV QUEEN108</t>
   </si>
   <si>
     <t>RPROCL1</t>
@@ -28,22 +28,10 @@
     <t>2</t>
   </si>
   <si>
-    <t>15</t>
+    <t>27</t>
   </si>
   <si>
     <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20134511</t>
-  </si>
-  <si>
-    <t>AICE CLSC CHO ALMD90</t>
-  </si>
-  <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
   </si>
 </sst>
 </file>
@@ -436,7 +424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -486,26 +474,6 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/RPROCL1.xlsx
+++ b/E/RPROCL1.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
   <si>
     <t/>
   </si>
   <si>
-    <t>20094387</t>
-  </si>
-  <si>
-    <t>CRNETTO SLV QUEEN108</t>
+    <t>10037640</t>
+  </si>
+  <si>
+    <t>WALL'S FEAST VNILA65</t>
   </si>
   <si>
     <t>RPROCL1</t>
@@ -28,10 +28,31 @@
     <t>2</t>
   </si>
   <si>
-    <t>27</t>
+    <t>45</t>
   </si>
   <si>
     <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10037632</t>
+  </si>
+  <si>
+    <t>WALL'S FEAST CKLT.65</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>20135228</t>
+  </si>
+  <si>
+    <t>AICE CRISPY BALLS 65</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
   </si>
 </sst>
 </file>
@@ -424,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -474,6 +495,46 @@
         <v>6</v>
       </c>
     </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/RPROCL1.xlsx
+++ b/E/RPROCL1.xlsx
@@ -11,29 +11,65 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="32">
   <si>
     <t/>
   </si>
   <si>
+    <t>20113120</t>
+  </si>
+  <si>
+    <t>AICE CHOCO ALMOND 90</t>
+  </si>
+  <si>
+    <t>RPROCL1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20072317</t>
+  </si>
+  <si>
+    <t>CORNETTO OREO 110</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>10005038</t>
+  </si>
+  <si>
+    <t>WALLS PPL CHO-VNL 90</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>10005039</t>
+  </si>
+  <si>
+    <t>WALLS PPL STW-VNL 90</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
     <t>10037640</t>
   </si>
   <si>
     <t>WALL'S FEAST VNILA65</t>
   </si>
   <si>
-    <t>RPROCL1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>45</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
     <t>10037632</t>
   </si>
   <si>
@@ -43,6 +79,27 @@
     <t>46</t>
   </si>
   <si>
+    <t>20129821</t>
+  </si>
+  <si>
+    <t>MAGNUM MATCHA.CRBL80</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20134511</t>
+  </si>
+  <si>
+    <t>AICE CLSC CHO ALMD90</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
     <t>20135228</t>
   </si>
   <si>
@@ -50,9 +107,6 @@
   </si>
   <si>
     <t>93</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
   </si>
 </sst>
 </file>
@@ -445,17 +499,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -474,8 +529,14 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -491,11 +552,11 @@
       <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -511,11 +572,11 @@
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -531,8 +592,128 @@
       <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/E/RPROCL1.xlsx
+++ b/E/RPROCL1.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="23">
   <si>
     <t/>
   </si>
@@ -61,24 +61,6 @@
     <t>33</t>
   </si>
   <si>
-    <t>10037640</t>
-  </si>
-  <si>
-    <t>WALL'S FEAST VNILA65</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>10037632</t>
-  </si>
-  <si>
-    <t>WALL'S FEAST CKLT.65</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
     <t>20129821</t>
   </si>
   <si>
@@ -98,15 +80,6 @@
   </si>
   <si>
     <t>91</t>
-  </si>
-  <si>
-    <t>20135228</t>
-  </si>
-  <si>
-    <t>AICE CRISPY BALLS 65</t>
-  </si>
-  <si>
-    <t>93</t>
   </si>
 </sst>
 </file>
@@ -499,18 +472,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -529,14 +501,8 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -552,11 +518,11 @@
       <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -572,11 +538,11 @@
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -592,11 +558,11 @@
       <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -612,11 +578,11 @@
       <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -632,16 +598,16 @@
       <c r="E6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>6</v>
+      <c r="F6" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -650,70 +616,10 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>25</v>
+      <c r="F7" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/E/RPROCL1.xlsx
+++ b/E/RPROCL1.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
   <si>
     <t/>
   </si>
   <si>
-    <t>20113120</t>
-  </si>
-  <si>
-    <t>AICE CHOCO ALMOND 90</t>
+    <t>20132330</t>
+  </si>
+  <si>
+    <t>AICE HSTERIA PEACH70</t>
   </si>
   <si>
     <t>RPROCL1</t>
@@ -28,58 +28,10 @@
     <t>2</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20072317</t>
-  </si>
-  <si>
-    <t>CORNETTO OREO 110</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>10005038</t>
-  </si>
-  <si>
-    <t>WALLS PPL CHO-VNL 90</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>10005039</t>
-  </si>
-  <si>
-    <t>WALLS PPL STW-VNL 90</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>20129821</t>
-  </si>
-  <si>
-    <t>MAGNUM MATCHA.CRBL80</t>
-  </si>
-  <si>
-    <t>47</t>
+    <t>71</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20134511</t>
-  </si>
-  <si>
-    <t>AICE CLSC CHO ALMD90</t>
-  </si>
-  <si>
-    <t>91</t>
   </si>
 </sst>
 </file>
@@ -472,7 +424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -522,106 +474,6 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/RPROCL1.xlsx
+++ b/E/RPROCL1.xlsx
@@ -11,21 +11,39 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
   <si>
     <t/>
   </si>
   <si>
+    <t>20032368</t>
+  </si>
+  <si>
+    <t>WALL'S MAGNUM ALMD80</t>
+  </si>
+  <si>
+    <t>RPROCL1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20032366</t>
+  </si>
+  <si>
+    <t>WALL'S MAGNUM CLAS80</t>
+  </si>
+  <si>
     <t>20132330</t>
   </si>
   <si>
     <t>AICE HSTERIA PEACH70</t>
-  </si>
-  <si>
-    <t>RPROCL1</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>71</t>
@@ -424,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -474,6 +492,46 @@
         <v>6</v>
       </c>
     </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/RPROCL1.xlsx
+++ b/E/RPROCL1.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
   <si>
     <t/>
   </si>
@@ -38,18 +38,6 @@
   </si>
   <si>
     <t>WALL'S MAGNUM CLAS80</t>
-  </si>
-  <si>
-    <t>20132330</t>
-  </si>
-  <si>
-    <t>AICE HSTERIA PEACH70</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
   </si>
 </sst>
 </file>
@@ -442,13 +430,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="5" max="5" width="4" customWidth="1"/>
+    <col min="4" max="5" width="3" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -512,26 +499,6 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/RPROCL1.xlsx
+++ b/E/RPROCL1.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
   <si>
     <t/>
   </si>
   <si>
-    <t>20032368</t>
-  </si>
-  <si>
-    <t>WALL'S MAGNUM ALMD80</t>
+    <t>20094387</t>
+  </si>
+  <si>
+    <t>CRNETTO SLV QUEEN108</t>
   </si>
   <si>
     <t>RPROCL1</t>
@@ -28,16 +28,10 @@
     <t>2</t>
   </si>
   <si>
-    <t>1</t>
+    <t>27</t>
   </si>
   <si>
     <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20032366</t>
-  </si>
-  <si>
-    <t>WALL'S MAGNUM CLAS80</t>
   </si>
 </sst>
 </file>
@@ -430,12 +424,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="4" max="5" width="3" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -476,26 +471,6 @@
         <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/E/RPROCL1.xlsx
+++ b/E/RPROCL1.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
   <si>
     <t/>
   </si>
   <si>
-    <t>20094387</t>
-  </si>
-  <si>
-    <t>CRNETTO SLV QUEEN108</t>
+    <t>10005038</t>
+  </si>
+  <si>
+    <t>WALLS PPL CHO-VNL 90</t>
   </si>
   <si>
     <t>RPROCL1</t>
@@ -28,10 +28,19 @@
     <t>2</t>
   </si>
   <si>
-    <t>27</t>
+    <t>32</t>
   </si>
   <si>
     <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10005039</t>
+  </si>
+  <si>
+    <t>WALLS PPL STW-VNL 90</t>
+  </si>
+  <si>
+    <t>33</t>
   </si>
 </sst>
 </file>
@@ -424,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -474,6 +483,26 @@
         <v>6</v>
       </c>
     </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
